--- a/artfynd/A 39974-2019 artfynd.xlsx
+++ b/artfynd/A 39974-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39974-2019 artfynd.xlsx
+++ b/artfynd/A 39974-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,6 +912,135 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122447932</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57394</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Slaktplatsen, Enköpings-Näs, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>613704</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6603573</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Enköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Enköpings-Näs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Alla satt i samma träd på hygget ca 500m söder kyrkan. Tillägg från besök på platsen den 1/3. Stora mängder slaktavfall från jakt ligger helt öppet. I så stora koncentrationer risk för blyförgiftning av toppredatorer, örn, vråk, korp, räv</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Torbjörn Larsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Torbjörn Larsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39974-2019 artfynd.xlsx
+++ b/artfynd/A 39974-2019 artfynd.xlsx
@@ -914,7 +914,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122447932</v>
+        <v>122447958</v>
       </c>
       <c r="B4" t="n">
         <v>57394</v>
@@ -949,14 +949,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Alla satt i samma träd på hygget ca 500m söder kyrkan. Tillägg från besök på platsen den 1/3. Stora mängder slaktavfall från jakt ligger helt öppet. I så stora koncentrationer risk för blyförgiftning av toppredatorer, örn, vråk, korp, räv</t>
+          <t>Sågs flyga vid samma hygge, ca 500m söder kyrkan, som tidigare på morgonen. Tillägg från besök på platsen den 1/3; Stora mängder slaktavfall från jakt ligger helt öppet. I så stora koncentrationer risk för blyförgiftning av toppredatorer, örn, vråk, korp, räv</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 39974-2019 artfynd.xlsx
+++ b/artfynd/A 39974-2019 artfynd.xlsx
@@ -914,7 +914,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122447958</v>
+        <v>122549759</v>
       </c>
       <c r="B4" t="n">
         <v>57394</v>
@@ -949,14 +949,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -996,27 +996,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Sågs flyga vid samma hygge, ca 500m söder kyrkan, som tidigare på morgonen. Tillägg från besök på platsen den 1/3; Stora mängder slaktavfall från jakt ligger helt öppet. I så stora koncentrationer risk för blyförgiftning av toppredatorer, örn, vråk, korp, räv</t>
+          <t>Tillägg efter besök på platsen 1/3: Stora mängder slaktavfall från jakt ligger helt öppet. I så stora koncentrationer risk för blyförgiftning av toppredatorer, örn, vråk, korp, räv Vid hygget ca 500m söder kyrkan. Samma plats som förra veckan. 2 satt i samma träd på hygget och 2 andra  sågs samtidigt flyga vid samma hygge störda av ca 10 korp och gråkråka.  Kanske ligger det ett trafikdödat vilt längre in på hugget.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 39974-2019 artfynd.xlsx
+++ b/artfynd/A 39974-2019 artfynd.xlsx
@@ -914,7 +914,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122549759</v>
+        <v>122447958</v>
       </c>
       <c r="B4" t="n">
         <v>57394</v>
@@ -949,14 +949,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -996,27 +996,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Tillägg efter besök på platsen 1/3: Stora mängder slaktavfall från jakt ligger helt öppet. I så stora koncentrationer risk för blyförgiftning av toppredatorer, örn, vråk, korp, räv Vid hygget ca 500m söder kyrkan. Samma plats som förra veckan. 2 satt i samma träd på hygget och 2 andra  sågs samtidigt flyga vid samma hygge störda av ca 10 korp och gråkråka.  Kanske ligger det ett trafikdödat vilt längre in på hugget.</t>
+          <t>Sågs flyga vid samma hygge, ca 500m söder kyrkan, som tidigare på morgonen. Tillägg från besök på platsen den 1/3; Stora mängder slaktavfall från jakt ligger helt öppet. I så stora koncentrationer risk för blyförgiftning av toppredatorer, örn, vråk, korp, räv</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 39974-2019 artfynd.xlsx
+++ b/artfynd/A 39974-2019 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>122447958</v>
       </c>
       <c r="B4" t="n">
-        <v>57394</v>
+        <v>57397</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 39974-2019 artfynd.xlsx
+++ b/artfynd/A 39974-2019 artfynd.xlsx
@@ -914,7 +914,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122447958</v>
+        <v>122549759</v>
       </c>
       <c r="B4" t="n">
         <v>57397</v>
@@ -949,14 +949,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -996,27 +996,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Sågs flyga vid samma hygge, ca 500m söder kyrkan, som tidigare på morgonen. Tillägg från besök på platsen den 1/3; Stora mängder slaktavfall från jakt ligger helt öppet. I så stora koncentrationer risk för blyförgiftning av toppredatorer, örn, vråk, korp, räv</t>
+          <t>Tillägg efter besök på platsen 1/3: Stora mängder slaktavfall från jakt ligger helt öppet. I så stora koncentrationer risk för blyförgiftning av toppredatorer, örn, vråk, korp, räv Vid hygget ca 500m söder kyrkan. Samma plats som förra veckan. 2 satt i samma träd på hygget och 2 andra  sågs samtidigt flyga vid samma hygge störda av ca 10 korp och gråkråka.  Kanske ligger det ett trafikdödat vilt längre in på hugget.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 39974-2019 artfynd.xlsx
+++ b/artfynd/A 39974-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113741331</v>
+        <v>122549759</v>
       </c>
       <c r="B3" t="n">
-        <v>57181</v>
+        <v>57397</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,23 +829,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Enköping, Upl</t>
+          <t>Slaktplatsen, Enköpings-Näs, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613657</v>
+        <v>613704</v>
       </c>
       <c r="R3" t="n">
-        <v>6603528</v>
+        <v>6603573</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,22 +876,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-12-24</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-12-24</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Tillägg efter besök på platsen 1/3: Stora mängder slaktavfall från jakt ligger helt öppet. I så stora koncentrationer risk för blyförgiftning av toppredatorer, örn, vråk, korp, räv Vid hygget ca 500m söder kyrkan. Samma plats som förra veckan. 2 satt i samma träd på hygget och 2 andra  sågs samtidigt flyga vid samma hygge störda av ca 10 korp och gråkråka.  Kanske ligger det ett trafikdödat vilt längre in på hugget.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,144 +911,15 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Grabs</t>
+          <t>Torbjörn Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Grabs</t>
+          <t>Torbjörn Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>122549759</v>
-      </c>
-      <c r="B4" t="n">
-        <v>57397</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>100067</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Havsörn</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Haliaeetus albicilla</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Slaktplatsen, Enköpings-Näs, Upl</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>613704</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6603573</v>
-      </c>
-      <c r="S4" t="n">
-        <v>25</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Enköping</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Enköpings-Näs</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025-02-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2025-02-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Tillägg efter besök på platsen 1/3: Stora mängder slaktavfall från jakt ligger helt öppet. I så stora koncentrationer risk för blyförgiftning av toppredatorer, örn, vråk, korp, räv Vid hygget ca 500m söder kyrkan. Samma plats som förra veckan. 2 satt i samma träd på hygget och 2 andra  sågs samtidigt flyga vid samma hygge störda av ca 10 korp och gråkråka.  Kanske ligger det ett trafikdödat vilt längre in på hugget.</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Torbjörn Larsson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Torbjörn Larsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
